--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N69_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N69_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.57338734438242</v>
+        <v>5.130675443462144</v>
       </c>
       <c r="D2" t="n">
-        <v>27.55911889786179</v>
+        <v>4.47835682090254</v>
       </c>
       <c r="E2" t="n">
-        <v>8.774442887282691</v>
+        <v>1.425846969183437</v>
       </c>
       <c r="F2" t="n">
-        <v>9.734899833558165</v>
+        <v>1.581921222953202</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.29157831481315</v>
+        <v>4.434881476157138</v>
       </c>
       <c r="D3" t="n">
-        <v>26.90863599958242</v>
+        <v>4.372653349932142</v>
       </c>
       <c r="E3" t="n">
-        <v>8.774442887282691</v>
+        <v>1.425846969183437</v>
       </c>
       <c r="F3" t="n">
-        <v>9.734899833558165</v>
+        <v>1.581921222953202</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.89722113015396</v>
+        <v>4.370798433650018</v>
       </c>
       <c r="D4" t="n">
-        <v>26.99833924563498</v>
+        <v>4.387230127415685</v>
       </c>
       <c r="E4" t="n">
-        <v>8.774442887282691</v>
+        <v>1.425846969183437</v>
       </c>
       <c r="F4" t="n">
-        <v>9.734899833558165</v>
+        <v>1.581921222953202</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>6.028850723577045</v>
+        <v>0.9796882425812699</v>
       </c>
       <c r="D5" t="n">
-        <v>5.804130038880315</v>
+        <v>0.9431711313180512</v>
       </c>
       <c r="E5" t="n">
-        <v>8.774442887282691</v>
+        <v>1.425846969183437</v>
       </c>
       <c r="F5" t="n">
-        <v>9.734899833558165</v>
+        <v>1.581921222953202</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>18.82855082993855</v>
+        <v>3.059639509865015</v>
       </c>
       <c r="D6" t="n">
-        <v>13.28323923011418</v>
+        <v>2.158526374893555</v>
       </c>
       <c r="E6" t="n">
-        <v>8.774442887282691</v>
+        <v>1.425846969183437</v>
       </c>
       <c r="F6" t="n">
-        <v>9.734899833558165</v>
+        <v>1.581921222953202</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>15.12357626588822</v>
+        <v>2.457581143206835</v>
       </c>
       <c r="D7" t="n">
-        <v>2.592097883360147</v>
+        <v>0.4212159060460238</v>
       </c>
       <c r="E7" t="n">
-        <v>8.774442887282691</v>
+        <v>1.425846969183437</v>
       </c>
       <c r="F7" t="n">
-        <v>9.734899833558165</v>
+        <v>1.581921222953202</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>10.74409270812167</v>
+        <v>1.745915065069772</v>
       </c>
       <c r="D8" t="n">
-        <v>20.09007494040555</v>
+        <v>3.264637177815902</v>
       </c>
       <c r="E8" t="n">
-        <v>8.774442887282691</v>
+        <v>1.425846969183437</v>
       </c>
       <c r="F8" t="n">
-        <v>9.734899833558165</v>
+        <v>1.581921222953202</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
